--- a/pesaje/analytica/Report/Lote-Export-Pesaje-Base.xlsx
+++ b/pesaje/analytica/Report/Lote-Export-Pesaje-Base.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\projects\minersoft-projects\minersoft\acopio-project-configuration\pesaje\analytica\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3841D79-160B-4480-9F1B-326A80C28B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE30BA40-9031-4860-9AB4-AAF4DD679DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>Analytica Mineral Services Sac</t>
   </si>
@@ -111,10 +111,16 @@
     <t>SACOS SEGÚN MINERO</t>
   </si>
   <si>
-    <t>ESTADO ACTA DE CONFORMIDAD</t>
-  </si>
-  <si>
-    <t>NUMERO ACTA CONFORMIDAD</t>
+    <t>GUARDIA</t>
+  </si>
+  <si>
+    <t>TURNO</t>
+  </si>
+  <si>
+    <t>ESTADO ACTA CONFORMIDAD</t>
+  </si>
+  <si>
+    <t>N° ACTA CONFORMIDAD</t>
   </si>
 </sst>
 </file>
@@ -125,7 +131,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-&quot;S/ &quot;* #,##0.00_-;&quot;-S/ &quot;* #,##0.00_-;_-&quot;S/ &quot;* \-??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -581,7 +587,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AW11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="13.6640625" style="4" customWidth="1"/>
     <col min="2" max="2" width="19.5546875" style="4" customWidth="1"/>
@@ -596,9 +602,11 @@
     <col min="12" max="24" width="24.6640625" style="4" customWidth="1"/>
     <col min="25" max="25" width="42.77734375" customWidth="1"/>
     <col min="26" max="26" width="40.33203125" customWidth="1"/>
+    <col min="27" max="27" width="29.33203125" customWidth="1"/>
+    <col min="28" max="28" width="38.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:49">
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -649,7 +657,7 @@
       <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
     </row>
-    <row r="2" spans="1:49" ht="48.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:49" ht="48.75" customHeight="1">
       <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
@@ -702,7 +710,7 @@
       <c r="AV2" s="1"/>
       <c r="AW2" s="1"/>
     </row>
-    <row r="3" spans="1:49" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:49" ht="22.5" customHeight="1">
       <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
@@ -755,7 +763,7 @@
       <c r="AV3" s="1"/>
       <c r="AW3" s="1"/>
     </row>
-    <row r="4" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:49" ht="15.75" customHeight="1">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -806,7 +814,7 @@
       <c r="AV4" s="1"/>
       <c r="AW4" s="1"/>
     </row>
-    <row r="5" spans="1:49" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:49" ht="15.6">
       <c r="A5" s="8"/>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -819,7 +827,7 @@
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
     </row>
-    <row r="6" spans="1:49" ht="18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:49" ht="18">
       <c r="A6" s="9"/>
       <c r="B6" s="10" t="s">
         <v>2</v>
@@ -832,7 +840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:49" ht="18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:49" ht="18">
       <c r="A7" s="9"/>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -845,7 +853,7 @@
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
     </row>
-    <row r="8" spans="1:49" s="11" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:49" s="11" customFormat="1" ht="28.8">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
@@ -871,62 +879,68 @@
         <v>13</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="L8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="P8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="R8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="U8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="V8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="X8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="W8" s="2" t="s">
+      <c r="Y8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="X8" s="2" t="s">
+      <c r="Z8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="Y8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>29</v>
+      <c r="AA8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:49" s="4" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:49" s="4" customFormat="1"/>
+    <row r="11" spans="1:49">
       <c r="F11" s="4" t="s">
         <v>9</v>
       </c>
